--- a/results/excel/result4.xlsx
+++ b/results/excel/result4.xlsx
@@ -466,63 +466,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>495817671</v>
+        <v>495403620</v>
       </c>
       <c r="C2" t="n">
-        <v>9630806627</v>
+        <v>9628223555</v>
       </c>
       <c r="D2" t="n">
-        <v>584</v>
+        <v>2079</v>
       </c>
       <c r="E2" t="n">
         <v>610.08</v>
       </c>
       <c r="F2" t="n">
-        <v>9850</v>
+        <v>6664</v>
       </c>
       <c r="G2" t="n">
-        <v>688</v>
+        <v>822</v>
       </c>
       <c r="H2" t="n">
-        <v>2322</v>
+        <v>2659</v>
       </c>
       <c r="I2" t="n">
-        <v>127</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C3" t="n">
-        <v>9630806627</v>
+        <v>1841014603</v>
       </c>
       <c r="D3" t="n">
-        <v>1853</v>
+        <v>5330</v>
       </c>
       <c r="E3" t="n">
         <v>610.08</v>
       </c>
       <c r="F3" t="n">
-        <v>9850</v>
+        <v>3063</v>
       </c>
       <c r="G3" t="n">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="H3" t="n">
-        <v>2322</v>
+        <v>2516</v>
       </c>
       <c r="I3" t="n">
-        <v>127</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4">
@@ -532,276 +532,276 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>495817671</v>
+        <v>525368335</v>
       </c>
       <c r="C4" t="n">
-        <v>9630806627</v>
+        <v>9811363528</v>
       </c>
       <c r="D4" t="n">
-        <v>5696</v>
+        <v>1797</v>
       </c>
       <c r="E4" t="n">
         <v>610.08</v>
       </c>
       <c r="F4" t="n">
-        <v>9850</v>
+        <v>7754</v>
       </c>
       <c r="G4" t="n">
-        <v>688</v>
+        <v>1060</v>
       </c>
       <c r="H4" t="n">
-        <v>2322</v>
+        <v>4002</v>
       </c>
       <c r="I4" t="n">
-        <v>127</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>525368335</v>
+        <v>495817671</v>
       </c>
       <c r="C5" t="n">
-        <v>9811363528</v>
+        <v>9630806627</v>
       </c>
       <c r="D5" t="n">
-        <v>5167</v>
+        <v>3600</v>
       </c>
       <c r="E5" t="n">
         <v>610.08</v>
       </c>
       <c r="F5" t="n">
-        <v>6331</v>
+        <v>7035</v>
       </c>
       <c r="G5" t="n">
-        <v>1090</v>
+        <v>686</v>
       </c>
       <c r="H5" t="n">
-        <v>4134</v>
+        <v>2097</v>
       </c>
       <c r="I5" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C6" t="n">
-        <v>1841014603</v>
+        <v>4190988309</v>
       </c>
       <c r="D6" t="n">
-        <v>6149</v>
+        <v>4097</v>
       </c>
       <c r="E6" t="n">
         <v>610.08</v>
       </c>
       <c r="F6" t="n">
-        <v>3574</v>
+        <v>8500</v>
       </c>
       <c r="G6" t="n">
-        <v>719</v>
+        <v>582</v>
       </c>
       <c r="H6" t="n">
-        <v>2792</v>
+        <v>1919</v>
       </c>
       <c r="I6" t="n">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>495403620</v>
+        <v>525368335</v>
       </c>
       <c r="C7" t="n">
-        <v>8878077181</v>
+        <v>9811363528</v>
       </c>
       <c r="D7" t="n">
-        <v>5778</v>
+        <v>4039</v>
       </c>
       <c r="E7" t="n">
         <v>610.08</v>
       </c>
       <c r="F7" t="n">
-        <v>1371</v>
+        <v>7754</v>
       </c>
       <c r="G7" t="n">
-        <v>828</v>
+        <v>1060</v>
       </c>
       <c r="H7" t="n">
-        <v>2849</v>
+        <v>4002</v>
       </c>
       <c r="I7" t="n">
-        <v>163</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>63563817</v>
       </c>
       <c r="C8" t="n">
-        <v>4190988309</v>
+        <v>1841014603</v>
       </c>
       <c r="D8" t="n">
-        <v>6082</v>
+        <v>3485</v>
       </c>
       <c r="E8" t="n">
         <v>610.08</v>
       </c>
       <c r="F8" t="n">
-        <v>8026</v>
+        <v>3063</v>
       </c>
       <c r="G8" t="n">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="H8" t="n">
-        <v>3164</v>
+        <v>2516</v>
       </c>
       <c r="I8" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C9" t="n">
-        <v>1841014603</v>
+        <v>9628223555</v>
       </c>
       <c r="D9" t="n">
-        <v>3169</v>
+        <v>267</v>
       </c>
       <c r="E9" t="n">
         <v>610.08</v>
       </c>
       <c r="F9" t="n">
-        <v>3574</v>
+        <v>6664</v>
       </c>
       <c r="G9" t="n">
-        <v>719</v>
+        <v>822</v>
       </c>
       <c r="H9" t="n">
-        <v>2792</v>
+        <v>2659</v>
       </c>
       <c r="I9" t="n">
-        <v>126</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>525368335</v>
+        <v>495403620</v>
       </c>
       <c r="C10" t="n">
-        <v>9811363528</v>
+        <v>8878077181</v>
       </c>
       <c r="D10" t="n">
-        <v>4817</v>
+        <v>1607</v>
       </c>
       <c r="E10" t="n">
         <v>610.08</v>
       </c>
       <c r="F10" t="n">
-        <v>6331</v>
+        <v>1286</v>
       </c>
       <c r="G10" t="n">
-        <v>1090</v>
+        <v>938</v>
       </c>
       <c r="H10" t="n">
-        <v>4134</v>
+        <v>3864</v>
       </c>
       <c r="I10" t="n">
-        <v>152</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C11" t="n">
-        <v>8878077181</v>
+        <v>1841014603</v>
       </c>
       <c r="D11" t="n">
-        <v>1048</v>
+        <v>1567</v>
       </c>
       <c r="E11" t="n">
         <v>610.08</v>
       </c>
       <c r="F11" t="n">
-        <v>1371</v>
+        <v>3063</v>
       </c>
       <c r="G11" t="n">
-        <v>828</v>
+        <v>681</v>
       </c>
       <c r="H11" t="n">
-        <v>2849</v>
+        <v>2516</v>
       </c>
       <c r="I11" t="n">
-        <v>163</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C12" t="n">
-        <v>8878077181</v>
+        <v>4190988309</v>
       </c>
       <c r="D12" t="n">
-        <v>1048</v>
+        <v>5649</v>
       </c>
       <c r="E12" t="n">
         <v>610.08</v>
       </c>
       <c r="F12" t="n">
-        <v>1371</v>
+        <v>8500</v>
       </c>
       <c r="G12" t="n">
-        <v>828</v>
+        <v>582</v>
       </c>
       <c r="H12" t="n">
-        <v>2849</v>
+        <v>1919</v>
       </c>
       <c r="I12" t="n">
-        <v>163</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13">
@@ -811,96 +811,96 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C13" t="n">
         <v>4190988309</v>
       </c>
       <c r="D13" t="n">
-        <v>4177</v>
+        <v>2373</v>
       </c>
       <c r="E13" t="n">
         <v>610.08</v>
       </c>
       <c r="F13" t="n">
-        <v>8026</v>
+        <v>8500</v>
       </c>
       <c r="G13" t="n">
-        <v>671</v>
+        <v>582</v>
       </c>
       <c r="H13" t="n">
-        <v>3164</v>
+        <v>1919</v>
       </c>
       <c r="I13" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C14" t="n">
-        <v>4190988309</v>
+        <v>8878077181</v>
       </c>
       <c r="D14" t="n">
-        <v>5257</v>
+        <v>1607</v>
       </c>
       <c r="E14" t="n">
         <v>610.08</v>
       </c>
       <c r="F14" t="n">
-        <v>8026</v>
+        <v>1286</v>
       </c>
       <c r="G14" t="n">
-        <v>671</v>
+        <v>938</v>
       </c>
       <c r="H14" t="n">
-        <v>3164</v>
+        <v>3864</v>
       </c>
       <c r="I14" t="n">
-        <v>111</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C15" t="n">
-        <v>9811363528</v>
+        <v>1841014603</v>
       </c>
       <c r="D15" t="n">
-        <v>6488</v>
+        <v>5973</v>
       </c>
       <c r="E15" t="n">
         <v>610.08</v>
       </c>
       <c r="F15" t="n">
-        <v>6331</v>
+        <v>3063</v>
       </c>
       <c r="G15" t="n">
-        <v>1090</v>
+        <v>681</v>
       </c>
       <c r="H15" t="n">
-        <v>4134</v>
+        <v>2516</v>
       </c>
       <c r="I15" t="n">
-        <v>152</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -910,84 +910,84 @@
         <v>9628223555</v>
       </c>
       <c r="D16" t="n">
-        <v>6162</v>
+        <v>4188</v>
       </c>
       <c r="E16" t="n">
         <v>610.08</v>
       </c>
       <c r="F16" t="n">
-        <v>5150</v>
+        <v>6664</v>
       </c>
       <c r="G16" t="n">
-        <v>782</v>
+        <v>822</v>
       </c>
       <c r="H16" t="n">
-        <v>2900</v>
+        <v>2659</v>
       </c>
       <c r="I16" t="n">
-        <v>82</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>495817671</v>
+        <v>525368335</v>
       </c>
       <c r="C17" t="n">
-        <v>9630806627</v>
+        <v>9811363528</v>
       </c>
       <c r="D17" t="n">
-        <v>2390</v>
+        <v>3671</v>
       </c>
       <c r="E17" t="n">
         <v>610.08</v>
       </c>
       <c r="F17" t="n">
-        <v>9850</v>
+        <v>7754</v>
       </c>
       <c r="G17" t="n">
-        <v>688</v>
+        <v>1060</v>
       </c>
       <c r="H17" t="n">
-        <v>2322</v>
+        <v>4002</v>
       </c>
       <c r="I17" t="n">
-        <v>127</v>
+        <v>317</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>63563817</v>
+        <v>495817671</v>
       </c>
       <c r="C18" t="n">
-        <v>4190988309</v>
+        <v>9630806627</v>
       </c>
       <c r="D18" t="n">
-        <v>1651</v>
+        <v>3127</v>
       </c>
       <c r="E18" t="n">
         <v>610.08</v>
       </c>
       <c r="F18" t="n">
-        <v>8026</v>
+        <v>7035</v>
       </c>
       <c r="G18" t="n">
-        <v>671</v>
+        <v>686</v>
       </c>
       <c r="H18" t="n">
-        <v>3164</v>
+        <v>2097</v>
       </c>
       <c r="I18" t="n">
-        <v>111</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19">
@@ -997,96 +997,96 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C19" t="n">
-        <v>1841014603</v>
+        <v>9811363528</v>
       </c>
       <c r="D19" t="n">
-        <v>5353</v>
+        <v>2976</v>
       </c>
       <c r="E19" t="n">
         <v>610.08</v>
       </c>
       <c r="F19" t="n">
-        <v>3574</v>
+        <v>7754</v>
       </c>
       <c r="G19" t="n">
-        <v>719</v>
+        <v>1060</v>
       </c>
       <c r="H19" t="n">
-        <v>2792</v>
+        <v>4002</v>
       </c>
       <c r="I19" t="n">
-        <v>126</v>
+        <v>317</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>525368335</v>
+        <v>495817671</v>
       </c>
       <c r="C20" t="n">
-        <v>8878077181</v>
+        <v>9630806627</v>
       </c>
       <c r="D20" t="n">
-        <v>3989</v>
+        <v>6607</v>
       </c>
       <c r="E20" t="n">
         <v>610.08</v>
       </c>
       <c r="F20" t="n">
-        <v>1371</v>
+        <v>7035</v>
       </c>
       <c r="G20" t="n">
-        <v>828</v>
+        <v>686</v>
       </c>
       <c r="H20" t="n">
-        <v>2849</v>
+        <v>2097</v>
       </c>
       <c r="I20" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C21" t="n">
-        <v>8878077181</v>
+        <v>4190988309</v>
       </c>
       <c r="D21" t="n">
-        <v>1607</v>
+        <v>2706</v>
       </c>
       <c r="E21" t="n">
-        <v>610.08</v>
+        <v>304.94</v>
       </c>
       <c r="F21" t="n">
-        <v>1371</v>
+        <v>4249</v>
       </c>
       <c r="G21" t="n">
-        <v>828</v>
+        <v>291</v>
       </c>
       <c r="H21" t="n">
-        <v>2849</v>
+        <v>959</v>
       </c>
       <c r="I21" t="n">
-        <v>163</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1096,239 +1096,239 @@
         <v>1841014603</v>
       </c>
       <c r="D22" t="n">
-        <v>5973</v>
+        <v>6364</v>
       </c>
       <c r="E22" t="n">
         <v>610.08</v>
       </c>
       <c r="F22" t="n">
-        <v>3574</v>
+        <v>3063</v>
       </c>
       <c r="G22" t="n">
-        <v>719</v>
+        <v>681</v>
       </c>
       <c r="H22" t="n">
-        <v>2792</v>
+        <v>2516</v>
       </c>
       <c r="I22" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>525368335</v>
+        <v>495403620</v>
       </c>
       <c r="C23" t="n">
-        <v>9811363528</v>
+        <v>9630806627</v>
       </c>
       <c r="D23" t="n">
-        <v>6269</v>
+        <v>1575</v>
       </c>
       <c r="E23" t="n">
         <v>610.08</v>
       </c>
       <c r="F23" t="n">
-        <v>6331</v>
+        <v>7035</v>
       </c>
       <c r="G23" t="n">
-        <v>1090</v>
+        <v>686</v>
       </c>
       <c r="H23" t="n">
-        <v>4134</v>
+        <v>2097</v>
       </c>
       <c r="I23" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>495817671</v>
+        <v>495403620</v>
       </c>
       <c r="C24" t="n">
-        <v>1841014603</v>
+        <v>9628223555</v>
       </c>
       <c r="D24" t="n">
-        <v>2892</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
         <v>610.08</v>
       </c>
       <c r="F24" t="n">
-        <v>3574</v>
+        <v>6664</v>
       </c>
       <c r="G24" t="n">
-        <v>719</v>
+        <v>822</v>
       </c>
       <c r="H24" t="n">
-        <v>2792</v>
+        <v>2659</v>
       </c>
       <c r="I24" t="n">
-        <v>126</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C25" t="n">
-        <v>1841014603</v>
+        <v>8878077181</v>
       </c>
       <c r="D25" t="n">
-        <v>2789</v>
+        <v>1607</v>
       </c>
       <c r="E25" t="n">
         <v>610.08</v>
       </c>
       <c r="F25" t="n">
-        <v>3574</v>
+        <v>1286</v>
       </c>
       <c r="G25" t="n">
-        <v>719</v>
+        <v>938</v>
       </c>
       <c r="H25" t="n">
-        <v>2792</v>
+        <v>3864</v>
       </c>
       <c r="I25" t="n">
-        <v>126</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>63563817</v>
+        <v>495817671</v>
       </c>
       <c r="C26" t="n">
-        <v>4190988309</v>
+        <v>9630806627</v>
       </c>
       <c r="D26" t="n">
-        <v>2706</v>
+        <v>794</v>
       </c>
       <c r="E26" t="n">
         <v>610.08</v>
       </c>
       <c r="F26" t="n">
-        <v>8026</v>
+        <v>7035</v>
       </c>
       <c r="G26" t="n">
-        <v>671</v>
+        <v>686</v>
       </c>
       <c r="H26" t="n">
-        <v>3164</v>
+        <v>2097</v>
       </c>
       <c r="I26" t="n">
-        <v>111</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>63563817</v>
+        <v>495817671</v>
       </c>
       <c r="C27" t="n">
-        <v>1841014603</v>
+        <v>9630806627</v>
       </c>
       <c r="D27" t="n">
-        <v>5973</v>
+        <v>3936</v>
       </c>
       <c r="E27" t="n">
         <v>610.08</v>
       </c>
       <c r="F27" t="n">
-        <v>3574</v>
+        <v>7035</v>
       </c>
       <c r="G27" t="n">
-        <v>719</v>
+        <v>686</v>
       </c>
       <c r="H27" t="n">
-        <v>2792</v>
+        <v>2097</v>
       </c>
       <c r="I27" t="n">
-        <v>126</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>495403620</v>
+        <v>525368335</v>
       </c>
       <c r="C28" t="n">
-        <v>8878077181</v>
+        <v>9811363528</v>
       </c>
       <c r="D28" t="n">
-        <v>1048</v>
+        <v>5918</v>
       </c>
       <c r="E28" t="n">
         <v>610.08</v>
       </c>
       <c r="F28" t="n">
-        <v>1371</v>
+        <v>7754</v>
       </c>
       <c r="G28" t="n">
-        <v>828</v>
+        <v>1060</v>
       </c>
       <c r="H28" t="n">
-        <v>2849</v>
+        <v>4002</v>
       </c>
       <c r="I28" t="n">
-        <v>163</v>
+        <v>317</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>495817671</v>
+        <v>525368335</v>
       </c>
       <c r="C29" t="n">
-        <v>9630806627</v>
+        <v>8878077181</v>
       </c>
       <c r="D29" t="n">
-        <v>6119</v>
+        <v>3989</v>
       </c>
       <c r="E29" t="n">
         <v>610.08</v>
       </c>
       <c r="F29" t="n">
-        <v>9850</v>
+        <v>1286</v>
       </c>
       <c r="G29" t="n">
-        <v>688</v>
+        <v>938</v>
       </c>
       <c r="H29" t="n">
-        <v>2322</v>
+        <v>3864</v>
       </c>
       <c r="I29" t="n">
-        <v>127</v>
+        <v>231</v>
       </c>
     </row>
     <row r="30">
@@ -1338,251 +1338,251 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C30" t="n">
-        <v>4190988309</v>
+        <v>9811363528</v>
       </c>
       <c r="D30" t="n">
-        <v>4134</v>
+        <v>3392</v>
       </c>
       <c r="E30" t="n">
         <v>610.08</v>
       </c>
       <c r="F30" t="n">
-        <v>8026</v>
+        <v>7754</v>
       </c>
       <c r="G30" t="n">
-        <v>671</v>
+        <v>1060</v>
       </c>
       <c r="H30" t="n">
-        <v>3164</v>
+        <v>4002</v>
       </c>
       <c r="I30" t="n">
-        <v>111</v>
+        <v>317</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C31" t="n">
-        <v>4190988309</v>
+        <v>8878077181</v>
       </c>
       <c r="D31" t="n">
-        <v>5649</v>
+        <v>3989</v>
       </c>
       <c r="E31" t="n">
         <v>610.08</v>
       </c>
       <c r="F31" t="n">
-        <v>8026</v>
+        <v>1286</v>
       </c>
       <c r="G31" t="n">
-        <v>671</v>
+        <v>938</v>
       </c>
       <c r="H31" t="n">
-        <v>3164</v>
+        <v>3864</v>
       </c>
       <c r="I31" t="n">
-        <v>111</v>
+        <v>231</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>495817671</v>
+        <v>525368335</v>
       </c>
       <c r="C32" t="n">
-        <v>9630806627</v>
+        <v>8878077181</v>
       </c>
       <c r="D32" t="n">
-        <v>2152</v>
+        <v>3989</v>
       </c>
       <c r="E32" t="n">
         <v>610.08</v>
       </c>
       <c r="F32" t="n">
-        <v>9850</v>
+        <v>1286</v>
       </c>
       <c r="G32" t="n">
-        <v>688</v>
+        <v>938</v>
       </c>
       <c r="H32" t="n">
-        <v>2322</v>
+        <v>3864</v>
       </c>
       <c r="I32" t="n">
-        <v>127</v>
+        <v>231</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>525368335</v>
+        <v>495403620</v>
       </c>
       <c r="C33" t="n">
-        <v>9811363528</v>
+        <v>9628223555</v>
       </c>
       <c r="D33" t="n">
-        <v>2467</v>
+        <v>2004</v>
       </c>
       <c r="E33" t="n">
         <v>610.08</v>
       </c>
       <c r="F33" t="n">
-        <v>6331</v>
+        <v>6664</v>
       </c>
       <c r="G33" t="n">
-        <v>1090</v>
+        <v>822</v>
       </c>
       <c r="H33" t="n">
-        <v>4134</v>
+        <v>2659</v>
       </c>
       <c r="I33" t="n">
-        <v>152</v>
+        <v>165</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C34" t="n">
-        <v>8878077181</v>
+        <v>1841014603</v>
       </c>
       <c r="D34" t="n">
-        <v>1607</v>
+        <v>3732</v>
       </c>
       <c r="E34" t="n">
         <v>610.08</v>
       </c>
       <c r="F34" t="n">
-        <v>1371</v>
+        <v>3063</v>
       </c>
       <c r="G34" t="n">
-        <v>828</v>
+        <v>681</v>
       </c>
       <c r="H34" t="n">
-        <v>2849</v>
+        <v>2516</v>
       </c>
       <c r="I34" t="n">
-        <v>163</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>525368335</v>
       </c>
       <c r="C35" t="n">
-        <v>9628223555</v>
+        <v>8878077181</v>
       </c>
       <c r="D35" t="n">
-        <v>4706</v>
+        <v>3989</v>
       </c>
       <c r="E35" t="n">
         <v>610.08</v>
       </c>
       <c r="F35" t="n">
-        <v>5150</v>
+        <v>1286</v>
       </c>
       <c r="G35" t="n">
-        <v>782</v>
+        <v>938</v>
       </c>
       <c r="H35" t="n">
-        <v>2900</v>
+        <v>3864</v>
       </c>
       <c r="I35" t="n">
-        <v>82</v>
+        <v>231</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>495403620</v>
+        <v>525368335</v>
       </c>
       <c r="C36" t="n">
-        <v>9628223555</v>
+        <v>9811363528</v>
       </c>
       <c r="D36" t="n">
-        <v>3379</v>
+        <v>506</v>
       </c>
       <c r="E36" t="n">
         <v>610.08</v>
       </c>
       <c r="F36" t="n">
-        <v>5150</v>
+        <v>7754</v>
       </c>
       <c r="G36" t="n">
-        <v>782</v>
+        <v>1060</v>
       </c>
       <c r="H36" t="n">
-        <v>2900</v>
+        <v>4002</v>
       </c>
       <c r="I36" t="n">
-        <v>82</v>
+        <v>317</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C37" t="n">
-        <v>9630806627</v>
+        <v>1841014603</v>
       </c>
       <c r="D37" t="n">
-        <v>6133</v>
+        <v>4675</v>
       </c>
       <c r="E37" t="n">
         <v>610.08</v>
       </c>
       <c r="F37" t="n">
-        <v>9850</v>
+        <v>3063</v>
       </c>
       <c r="G37" t="n">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="H37" t="n">
-        <v>2322</v>
+        <v>2516</v>
       </c>
       <c r="I37" t="n">
-        <v>127</v>
+        <v>112</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1592,84 +1592,84 @@
         <v>9628223555</v>
       </c>
       <c r="D38" t="n">
-        <v>4560</v>
+        <v>4388</v>
       </c>
       <c r="E38" t="n">
-        <v>305.04</v>
+        <v>610.08</v>
       </c>
       <c r="F38" t="n">
-        <v>2575</v>
+        <v>6664</v>
       </c>
       <c r="G38" t="n">
-        <v>391</v>
+        <v>822</v>
       </c>
       <c r="H38" t="n">
-        <v>1450</v>
+        <v>2659</v>
       </c>
       <c r="I38" t="n">
-        <v>41</v>
+        <v>165</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>525368335</v>
+        <v>495817671</v>
       </c>
       <c r="C39" t="n">
-        <v>9811363528</v>
+        <v>9628223555</v>
       </c>
       <c r="D39" t="n">
-        <v>24</v>
+        <v>5259</v>
       </c>
       <c r="E39" t="n">
         <v>610.08</v>
       </c>
       <c r="F39" t="n">
-        <v>6331</v>
+        <v>6664</v>
       </c>
       <c r="G39" t="n">
-        <v>1090</v>
+        <v>822</v>
       </c>
       <c r="H39" t="n">
-        <v>4134</v>
+        <v>2659</v>
       </c>
       <c r="I39" t="n">
-        <v>152</v>
+        <v>165</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>495817671</v>
       </c>
       <c r="C40" t="n">
-        <v>9811363528</v>
+        <v>9630806627</v>
       </c>
       <c r="D40" t="n">
-        <v>848</v>
+        <v>1041</v>
       </c>
       <c r="E40" t="n">
         <v>610.08</v>
       </c>
       <c r="F40" t="n">
-        <v>6331</v>
+        <v>7035</v>
       </c>
       <c r="G40" t="n">
-        <v>1090</v>
+        <v>686</v>
       </c>
       <c r="H40" t="n">
-        <v>4134</v>
+        <v>2097</v>
       </c>
       <c r="I40" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/results/excel/result4.xlsx
+++ b/results/excel/result4.xlsx
@@ -466,32 +466,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C2" t="n">
-        <v>9628223555</v>
+        <v>2526158329</v>
       </c>
       <c r="D2" t="n">
-        <v>2079</v>
+        <v>2942</v>
       </c>
       <c r="E2" t="n">
         <v>610.08</v>
       </c>
       <c r="F2" t="n">
-        <v>6664</v>
+        <v>3422</v>
       </c>
       <c r="G2" t="n">
-        <v>822</v>
+        <v>646</v>
       </c>
       <c r="H2" t="n">
-        <v>2659</v>
+        <v>2278</v>
       </c>
       <c r="I2" t="n">
-        <v>165</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3">
@@ -501,183 +501,183 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C3" t="n">
-        <v>1841014603</v>
+        <v>9811363528</v>
       </c>
       <c r="D3" t="n">
-        <v>5330</v>
+        <v>4483</v>
       </c>
       <c r="E3" t="n">
         <v>610.08</v>
       </c>
       <c r="F3" t="n">
-        <v>3063</v>
+        <v>6441</v>
       </c>
       <c r="G3" t="n">
-        <v>681</v>
+        <v>900</v>
       </c>
       <c r="H3" t="n">
-        <v>2516</v>
+        <v>3409</v>
       </c>
       <c r="I3" t="n">
-        <v>112</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C4" t="n">
-        <v>9811363528</v>
+        <v>2526158329</v>
       </c>
       <c r="D4" t="n">
-        <v>1797</v>
+        <v>1385</v>
       </c>
       <c r="E4" t="n">
         <v>610.08</v>
       </c>
       <c r="F4" t="n">
-        <v>7754</v>
+        <v>3422</v>
       </c>
       <c r="G4" t="n">
-        <v>1060</v>
+        <v>646</v>
       </c>
       <c r="H4" t="n">
-        <v>4002</v>
+        <v>2278</v>
       </c>
       <c r="I4" t="n">
-        <v>317</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C5" t="n">
-        <v>9630806627</v>
+        <v>2526158329</v>
       </c>
       <c r="D5" t="n">
-        <v>3600</v>
+        <v>1277</v>
       </c>
       <c r="E5" t="n">
         <v>610.08</v>
       </c>
       <c r="F5" t="n">
-        <v>7035</v>
+        <v>3422</v>
       </c>
       <c r="G5" t="n">
-        <v>686</v>
+        <v>646</v>
       </c>
       <c r="H5" t="n">
-        <v>2097</v>
+        <v>2278</v>
       </c>
       <c r="I5" t="n">
-        <v>162</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>63563817</v>
       </c>
       <c r="C6" t="n">
-        <v>4190988309</v>
+        <v>1841014603</v>
       </c>
       <c r="D6" t="n">
-        <v>4097</v>
+        <v>2373</v>
       </c>
       <c r="E6" t="n">
         <v>610.08</v>
       </c>
       <c r="F6" t="n">
-        <v>8500</v>
+        <v>2922</v>
       </c>
       <c r="G6" t="n">
-        <v>582</v>
+        <v>602</v>
       </c>
       <c r="H6" t="n">
-        <v>1919</v>
+        <v>2208</v>
       </c>
       <c r="I6" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>525368335</v>
       </c>
       <c r="C7" t="n">
-        <v>9811363528</v>
+        <v>9628223555</v>
       </c>
       <c r="D7" t="n">
-        <v>4039</v>
+        <v>3222</v>
       </c>
       <c r="E7" t="n">
         <v>610.08</v>
       </c>
       <c r="F7" t="n">
-        <v>7754</v>
+        <v>6336</v>
       </c>
       <c r="G7" t="n">
-        <v>1060</v>
+        <v>745</v>
       </c>
       <c r="H7" t="n">
-        <v>4002</v>
+        <v>2912</v>
       </c>
       <c r="I7" t="n">
-        <v>317</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C8" t="n">
-        <v>1841014603</v>
+        <v>8878077181</v>
       </c>
       <c r="D8" t="n">
-        <v>3485</v>
+        <v>1048</v>
       </c>
       <c r="E8" t="n">
         <v>610.08</v>
       </c>
       <c r="F8" t="n">
-        <v>3063</v>
+        <v>1184</v>
       </c>
       <c r="G8" t="n">
-        <v>681</v>
+        <v>876</v>
       </c>
       <c r="H8" t="n">
-        <v>2516</v>
+        <v>3293</v>
       </c>
       <c r="I8" t="n">
-        <v>112</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9">
@@ -687,90 +687,90 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>495403620</v>
+        <v>525368335</v>
       </c>
       <c r="C9" t="n">
-        <v>9628223555</v>
+        <v>9811363528</v>
       </c>
       <c r="D9" t="n">
-        <v>267</v>
+        <v>6306</v>
       </c>
       <c r="E9" t="n">
         <v>610.08</v>
       </c>
       <c r="F9" t="n">
-        <v>6664</v>
+        <v>6441</v>
       </c>
       <c r="G9" t="n">
-        <v>822</v>
+        <v>900</v>
       </c>
       <c r="H9" t="n">
-        <v>2659</v>
+        <v>3409</v>
       </c>
       <c r="I9" t="n">
-        <v>165</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>495403620</v>
+        <v>495817671</v>
       </c>
       <c r="C10" t="n">
-        <v>8878077181</v>
+        <v>9630806627</v>
       </c>
       <c r="D10" t="n">
-        <v>1607</v>
+        <v>5679</v>
       </c>
       <c r="E10" t="n">
         <v>610.08</v>
       </c>
       <c r="F10" t="n">
-        <v>1286</v>
+        <v>6969</v>
       </c>
       <c r="G10" t="n">
-        <v>938</v>
+        <v>724</v>
       </c>
       <c r="H10" t="n">
-        <v>3864</v>
+        <v>2776</v>
       </c>
       <c r="I10" t="n">
-        <v>231</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C11" t="n">
-        <v>1841014603</v>
+        <v>8878077181</v>
       </c>
       <c r="D11" t="n">
-        <v>1567</v>
+        <v>1607</v>
       </c>
       <c r="E11" t="n">
         <v>610.08</v>
       </c>
       <c r="F11" t="n">
-        <v>3063</v>
+        <v>1184</v>
       </c>
       <c r="G11" t="n">
-        <v>681</v>
+        <v>876</v>
       </c>
       <c r="H11" t="n">
-        <v>2516</v>
+        <v>3293</v>
       </c>
       <c r="I11" t="n">
-        <v>112</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12">
@@ -780,96 +780,96 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63563817</v>
+        <v>495817671</v>
       </c>
       <c r="C12" t="n">
-        <v>4190988309</v>
+        <v>9628223555</v>
       </c>
       <c r="D12" t="n">
-        <v>5649</v>
+        <v>6210</v>
       </c>
       <c r="E12" t="n">
         <v>610.08</v>
       </c>
       <c r="F12" t="n">
-        <v>8500</v>
+        <v>6336</v>
       </c>
       <c r="G12" t="n">
-        <v>582</v>
+        <v>745</v>
       </c>
       <c r="H12" t="n">
-        <v>1919</v>
+        <v>2912</v>
       </c>
       <c r="I12" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>63563817</v>
       </c>
       <c r="C13" t="n">
-        <v>4190988309</v>
+        <v>2526158329</v>
       </c>
       <c r="D13" t="n">
-        <v>2373</v>
+        <v>5942</v>
       </c>
       <c r="E13" t="n">
         <v>610.08</v>
       </c>
       <c r="F13" t="n">
-        <v>8500</v>
+        <v>3422</v>
       </c>
       <c r="G13" t="n">
-        <v>582</v>
+        <v>646</v>
       </c>
       <c r="H13" t="n">
-        <v>1919</v>
+        <v>2278</v>
       </c>
       <c r="I13" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>495403620</v>
+        <v>495817671</v>
       </c>
       <c r="C14" t="n">
-        <v>8878077181</v>
+        <v>9630806627</v>
       </c>
       <c r="D14" t="n">
-        <v>1607</v>
+        <v>1041</v>
       </c>
       <c r="E14" t="n">
         <v>610.08</v>
       </c>
       <c r="F14" t="n">
-        <v>1286</v>
+        <v>6969</v>
       </c>
       <c r="G14" t="n">
-        <v>938</v>
+        <v>724</v>
       </c>
       <c r="H14" t="n">
-        <v>3864</v>
+        <v>2776</v>
       </c>
       <c r="I14" t="n">
-        <v>231</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -879,59 +879,59 @@
         <v>1841014603</v>
       </c>
       <c r="D15" t="n">
-        <v>5973</v>
+        <v>3169</v>
       </c>
       <c r="E15" t="n">
-        <v>610.08</v>
+        <v>304.94</v>
       </c>
       <c r="F15" t="n">
-        <v>3063</v>
+        <v>1461</v>
       </c>
       <c r="G15" t="n">
-        <v>681</v>
+        <v>301</v>
       </c>
       <c r="H15" t="n">
-        <v>2516</v>
+        <v>1104</v>
       </c>
       <c r="I15" t="n">
-        <v>112</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>495403620</v>
+        <v>495817671</v>
       </c>
       <c r="C16" t="n">
         <v>9628223555</v>
       </c>
       <c r="D16" t="n">
-        <v>4188</v>
+        <v>2370</v>
       </c>
       <c r="E16" t="n">
         <v>610.08</v>
       </c>
       <c r="F16" t="n">
-        <v>6664</v>
+        <v>6336</v>
       </c>
       <c r="G16" t="n">
-        <v>822</v>
+        <v>745</v>
       </c>
       <c r="H16" t="n">
-        <v>2659</v>
+        <v>2912</v>
       </c>
       <c r="I16" t="n">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -941,22 +941,22 @@
         <v>9811363528</v>
       </c>
       <c r="D17" t="n">
-        <v>3671</v>
+        <v>3431</v>
       </c>
       <c r="E17" t="n">
         <v>610.08</v>
       </c>
       <c r="F17" t="n">
-        <v>7754</v>
+        <v>6441</v>
       </c>
       <c r="G17" t="n">
-        <v>1060</v>
+        <v>900</v>
       </c>
       <c r="H17" t="n">
-        <v>4002</v>
+        <v>3409</v>
       </c>
       <c r="I17" t="n">
-        <v>317</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18">
@@ -972,59 +972,59 @@
         <v>9630806627</v>
       </c>
       <c r="D18" t="n">
-        <v>3127</v>
+        <v>815</v>
       </c>
       <c r="E18" t="n">
         <v>610.08</v>
       </c>
       <c r="F18" t="n">
-        <v>7035</v>
+        <v>6969</v>
       </c>
       <c r="G18" t="n">
-        <v>686</v>
+        <v>724</v>
       </c>
       <c r="H18" t="n">
-        <v>2097</v>
+        <v>2776</v>
       </c>
       <c r="I18" t="n">
-        <v>162</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>525368335</v>
+        <v>495403620</v>
       </c>
       <c r="C19" t="n">
-        <v>9811363528</v>
+        <v>8878077181</v>
       </c>
       <c r="D19" t="n">
-        <v>2976</v>
+        <v>1607</v>
       </c>
       <c r="E19" t="n">
         <v>610.08</v>
       </c>
       <c r="F19" t="n">
-        <v>7754</v>
+        <v>1184</v>
       </c>
       <c r="G19" t="n">
-        <v>1060</v>
+        <v>876</v>
       </c>
       <c r="H19" t="n">
-        <v>4002</v>
+        <v>3293</v>
       </c>
       <c r="I19" t="n">
-        <v>317</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1034,270 +1034,270 @@
         <v>9630806627</v>
       </c>
       <c r="D20" t="n">
-        <v>6607</v>
+        <v>1207</v>
       </c>
       <c r="E20" t="n">
         <v>610.08</v>
       </c>
       <c r="F20" t="n">
-        <v>7035</v>
+        <v>6969</v>
       </c>
       <c r="G20" t="n">
-        <v>686</v>
+        <v>724</v>
       </c>
       <c r="H20" t="n">
-        <v>2097</v>
+        <v>2776</v>
       </c>
       <c r="I20" t="n">
-        <v>162</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C21" t="n">
-        <v>4190988309</v>
+        <v>9628223555</v>
       </c>
       <c r="D21" t="n">
-        <v>2706</v>
+        <v>5703</v>
       </c>
       <c r="E21" t="n">
-        <v>304.94</v>
+        <v>610.08</v>
       </c>
       <c r="F21" t="n">
-        <v>4249</v>
+        <v>6336</v>
       </c>
       <c r="G21" t="n">
-        <v>291</v>
+        <v>745</v>
       </c>
       <c r="H21" t="n">
-        <v>959</v>
+        <v>2912</v>
       </c>
       <c r="I21" t="n">
-        <v>54</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C22" t="n">
-        <v>1841014603</v>
+        <v>9628223555</v>
       </c>
       <c r="D22" t="n">
-        <v>6364</v>
+        <v>5111</v>
       </c>
       <c r="E22" t="n">
         <v>610.08</v>
       </c>
       <c r="F22" t="n">
-        <v>3063</v>
+        <v>6336</v>
       </c>
       <c r="G22" t="n">
-        <v>681</v>
+        <v>745</v>
       </c>
       <c r="H22" t="n">
-        <v>2516</v>
+        <v>2912</v>
       </c>
       <c r="I22" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>495403620</v>
+        <v>525368335</v>
       </c>
       <c r="C23" t="n">
-        <v>9630806627</v>
+        <v>9811363528</v>
       </c>
       <c r="D23" t="n">
-        <v>1575</v>
+        <v>4202</v>
       </c>
       <c r="E23" t="n">
         <v>610.08</v>
       </c>
       <c r="F23" t="n">
-        <v>7035</v>
+        <v>6441</v>
       </c>
       <c r="G23" t="n">
-        <v>686</v>
+        <v>900</v>
       </c>
       <c r="H23" t="n">
-        <v>2097</v>
+        <v>3409</v>
       </c>
       <c r="I23" t="n">
-        <v>162</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>495403620</v>
       </c>
       <c r="C24" t="n">
-        <v>9628223555</v>
+        <v>8878077181</v>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>1048</v>
       </c>
       <c r="E24" t="n">
         <v>610.08</v>
       </c>
       <c r="F24" t="n">
-        <v>6664</v>
+        <v>1184</v>
       </c>
       <c r="G24" t="n">
-        <v>822</v>
+        <v>876</v>
       </c>
       <c r="H24" t="n">
-        <v>2659</v>
+        <v>3293</v>
       </c>
       <c r="I24" t="n">
-        <v>165</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>495403620</v>
+        <v>495817671</v>
       </c>
       <c r="C25" t="n">
-        <v>8878077181</v>
+        <v>9630806627</v>
       </c>
       <c r="D25" t="n">
-        <v>1607</v>
+        <v>4579</v>
       </c>
       <c r="E25" t="n">
         <v>610.08</v>
       </c>
       <c r="F25" t="n">
-        <v>1286</v>
+        <v>6969</v>
       </c>
       <c r="G25" t="n">
-        <v>938</v>
+        <v>724</v>
       </c>
       <c r="H25" t="n">
-        <v>3864</v>
+        <v>2776</v>
       </c>
       <c r="I25" t="n">
-        <v>231</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>495817671</v>
+        <v>525368335</v>
       </c>
       <c r="C26" t="n">
-        <v>9630806627</v>
+        <v>8878077181</v>
       </c>
       <c r="D26" t="n">
-        <v>794</v>
+        <v>3989</v>
       </c>
       <c r="E26" t="n">
         <v>610.08</v>
       </c>
       <c r="F26" t="n">
-        <v>7035</v>
+        <v>1184</v>
       </c>
       <c r="G26" t="n">
-        <v>686</v>
+        <v>876</v>
       </c>
       <c r="H26" t="n">
-        <v>2097</v>
+        <v>3293</v>
       </c>
       <c r="I26" t="n">
-        <v>162</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C27" t="n">
-        <v>9630806627</v>
+        <v>1841014603</v>
       </c>
       <c r="D27" t="n">
-        <v>3936</v>
+        <v>2373</v>
       </c>
       <c r="E27" t="n">
         <v>610.08</v>
       </c>
       <c r="F27" t="n">
-        <v>7035</v>
+        <v>2922</v>
       </c>
       <c r="G27" t="n">
-        <v>686</v>
+        <v>602</v>
       </c>
       <c r="H27" t="n">
-        <v>2097</v>
+        <v>2208</v>
       </c>
       <c r="I27" t="n">
-        <v>162</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>525368335</v>
+        <v>495817671</v>
       </c>
       <c r="C28" t="n">
-        <v>9811363528</v>
+        <v>9630806627</v>
       </c>
       <c r="D28" t="n">
-        <v>5918</v>
+        <v>3913</v>
       </c>
       <c r="E28" t="n">
         <v>610.08</v>
       </c>
       <c r="F28" t="n">
-        <v>7754</v>
+        <v>6969</v>
       </c>
       <c r="G28" t="n">
-        <v>1060</v>
+        <v>724</v>
       </c>
       <c r="H28" t="n">
-        <v>4002</v>
+        <v>2776</v>
       </c>
       <c r="I28" t="n">
-        <v>317</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29">
@@ -1310,56 +1310,56 @@
         <v>525368335</v>
       </c>
       <c r="C29" t="n">
-        <v>8878077181</v>
+        <v>9811363528</v>
       </c>
       <c r="D29" t="n">
-        <v>3989</v>
+        <v>3865</v>
       </c>
       <c r="E29" t="n">
         <v>610.08</v>
       </c>
       <c r="F29" t="n">
-        <v>1286</v>
+        <v>6441</v>
       </c>
       <c r="G29" t="n">
-        <v>938</v>
+        <v>900</v>
       </c>
       <c r="H29" t="n">
-        <v>3864</v>
+        <v>3409</v>
       </c>
       <c r="I29" t="n">
-        <v>231</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C30" t="n">
-        <v>9811363528</v>
+        <v>2526158329</v>
       </c>
       <c r="D30" t="n">
-        <v>3392</v>
+        <v>5700</v>
       </c>
       <c r="E30" t="n">
         <v>610.08</v>
       </c>
       <c r="F30" t="n">
-        <v>7754</v>
+        <v>3422</v>
       </c>
       <c r="G30" t="n">
-        <v>1060</v>
+        <v>646</v>
       </c>
       <c r="H30" t="n">
-        <v>4002</v>
+        <v>2278</v>
       </c>
       <c r="I30" t="n">
-        <v>317</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31">
@@ -1372,56 +1372,56 @@
         <v>525368335</v>
       </c>
       <c r="C31" t="n">
-        <v>8878077181</v>
+        <v>9811363528</v>
       </c>
       <c r="D31" t="n">
-        <v>3989</v>
+        <v>4453</v>
       </c>
       <c r="E31" t="n">
         <v>610.08</v>
       </c>
       <c r="F31" t="n">
-        <v>1286</v>
+        <v>6441</v>
       </c>
       <c r="G31" t="n">
-        <v>938</v>
+        <v>900</v>
       </c>
       <c r="H31" t="n">
-        <v>3864</v>
+        <v>3409</v>
       </c>
       <c r="I31" t="n">
-        <v>231</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>525368335</v>
+        <v>495403620</v>
       </c>
       <c r="C32" t="n">
         <v>8878077181</v>
       </c>
       <c r="D32" t="n">
-        <v>3989</v>
+        <v>1607</v>
       </c>
       <c r="E32" t="n">
         <v>610.08</v>
       </c>
       <c r="F32" t="n">
-        <v>1286</v>
+        <v>1184</v>
       </c>
       <c r="G32" t="n">
-        <v>938</v>
+        <v>876</v>
       </c>
       <c r="H32" t="n">
-        <v>3864</v>
+        <v>3293</v>
       </c>
       <c r="I32" t="n">
-        <v>231</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33">
@@ -1431,214 +1431,214 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>495403620</v>
+        <v>525368335</v>
       </c>
       <c r="C33" t="n">
-        <v>9628223555</v>
+        <v>8878077181</v>
       </c>
       <c r="D33" t="n">
-        <v>2004</v>
+        <v>3989</v>
       </c>
       <c r="E33" t="n">
         <v>610.08</v>
       </c>
       <c r="F33" t="n">
-        <v>6664</v>
+        <v>1184</v>
       </c>
       <c r="G33" t="n">
-        <v>822</v>
+        <v>876</v>
       </c>
       <c r="H33" t="n">
-        <v>2659</v>
+        <v>3293</v>
       </c>
       <c r="I33" t="n">
-        <v>165</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C34" t="n">
-        <v>1841014603</v>
+        <v>9811363528</v>
       </c>
       <c r="D34" t="n">
-        <v>3732</v>
+        <v>5873</v>
       </c>
       <c r="E34" t="n">
         <v>610.08</v>
       </c>
       <c r="F34" t="n">
-        <v>3063</v>
+        <v>6441</v>
       </c>
       <c r="G34" t="n">
-        <v>681</v>
+        <v>900</v>
       </c>
       <c r="H34" t="n">
-        <v>2516</v>
+        <v>3409</v>
       </c>
       <c r="I34" t="n">
-        <v>112</v>
+        <v>144</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>525368335</v>
+        <v>495817671</v>
       </c>
       <c r="C35" t="n">
-        <v>8878077181</v>
+        <v>9630806627</v>
       </c>
       <c r="D35" t="n">
-        <v>3989</v>
+        <v>6435</v>
       </c>
       <c r="E35" t="n">
         <v>610.08</v>
       </c>
       <c r="F35" t="n">
-        <v>1286</v>
+        <v>6969</v>
       </c>
       <c r="G35" t="n">
-        <v>938</v>
+        <v>724</v>
       </c>
       <c r="H35" t="n">
-        <v>3864</v>
+        <v>2776</v>
       </c>
       <c r="I35" t="n">
-        <v>231</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C36" t="n">
-        <v>9811363528</v>
+        <v>1841014603</v>
       </c>
       <c r="D36" t="n">
-        <v>506</v>
+        <v>5393</v>
       </c>
       <c r="E36" t="n">
         <v>610.08</v>
       </c>
       <c r="F36" t="n">
-        <v>7754</v>
+        <v>2922</v>
       </c>
       <c r="G36" t="n">
-        <v>1060</v>
+        <v>602</v>
       </c>
       <c r="H36" t="n">
-        <v>4002</v>
+        <v>2208</v>
       </c>
       <c r="I36" t="n">
-        <v>317</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>63563817</v>
       </c>
       <c r="C37" t="n">
-        <v>1841014603</v>
+        <v>2526158329</v>
       </c>
       <c r="D37" t="n">
-        <v>4675</v>
+        <v>6014</v>
       </c>
       <c r="E37" t="n">
         <v>610.08</v>
       </c>
       <c r="F37" t="n">
-        <v>3063</v>
+        <v>3422</v>
       </c>
       <c r="G37" t="n">
-        <v>681</v>
+        <v>646</v>
       </c>
       <c r="H37" t="n">
-        <v>2516</v>
+        <v>2278</v>
       </c>
       <c r="I37" t="n">
-        <v>112</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>495403620</v>
+        <v>525368335</v>
       </c>
       <c r="C38" t="n">
         <v>9628223555</v>
       </c>
       <c r="D38" t="n">
-        <v>4388</v>
+        <v>3769</v>
       </c>
       <c r="E38" t="n">
         <v>610.08</v>
       </c>
       <c r="F38" t="n">
-        <v>6664</v>
+        <v>6336</v>
       </c>
       <c r="G38" t="n">
-        <v>822</v>
+        <v>745</v>
       </c>
       <c r="H38" t="n">
-        <v>2659</v>
+        <v>2912</v>
       </c>
       <c r="I38" t="n">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C39" t="n">
-        <v>9628223555</v>
+        <v>2526158329</v>
       </c>
       <c r="D39" t="n">
-        <v>5259</v>
+        <v>1262</v>
       </c>
       <c r="E39" t="n">
         <v>610.08</v>
       </c>
       <c r="F39" t="n">
-        <v>6664</v>
+        <v>3422</v>
       </c>
       <c r="G39" t="n">
-        <v>822</v>
+        <v>646</v>
       </c>
       <c r="H39" t="n">
-        <v>2659</v>
+        <v>2278</v>
       </c>
       <c r="I39" t="n">
-        <v>165</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40">
@@ -1648,28 +1648,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>495817671</v>
+        <v>495403620</v>
       </c>
       <c r="C40" t="n">
-        <v>9630806627</v>
+        <v>9628223555</v>
       </c>
       <c r="D40" t="n">
-        <v>1041</v>
+        <v>4046</v>
       </c>
       <c r="E40" t="n">
         <v>610.08</v>
       </c>
       <c r="F40" t="n">
-        <v>7035</v>
+        <v>6336</v>
       </c>
       <c r="G40" t="n">
-        <v>686</v>
+        <v>745</v>
       </c>
       <c r="H40" t="n">
-        <v>2097</v>
+        <v>2912</v>
       </c>
       <c r="I40" t="n">
-        <v>162</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/results/excel/result4.xlsx
+++ b/results/excel/result4.xlsx
@@ -466,131 +466,131 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>63563817</v>
       </c>
       <c r="C2" t="n">
-        <v>2526158329</v>
+        <v>1841014603</v>
       </c>
       <c r="D2" t="n">
-        <v>2942</v>
+        <v>5307</v>
       </c>
       <c r="E2" t="n">
         <v>610.08</v>
       </c>
       <c r="F2" t="n">
-        <v>3422</v>
+        <v>2922</v>
       </c>
       <c r="G2" t="n">
-        <v>646</v>
+        <v>602</v>
       </c>
       <c r="H2" t="n">
-        <v>2278</v>
+        <v>2208</v>
       </c>
       <c r="I2" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>525368335</v>
+        <v>495403620</v>
       </c>
       <c r="C3" t="n">
-        <v>9811363528</v>
+        <v>9628223555</v>
       </c>
       <c r="D3" t="n">
-        <v>4483</v>
+        <v>3653</v>
       </c>
       <c r="E3" t="n">
         <v>610.08</v>
       </c>
       <c r="F3" t="n">
-        <v>6441</v>
+        <v>6336</v>
       </c>
       <c r="G3" t="n">
-        <v>900</v>
+        <v>745</v>
       </c>
       <c r="H3" t="n">
-        <v>3409</v>
+        <v>2912</v>
       </c>
       <c r="I3" t="n">
-        <v>144</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C4" t="n">
-        <v>2526158329</v>
+        <v>8878077181</v>
       </c>
       <c r="D4" t="n">
-        <v>1385</v>
+        <v>1607</v>
       </c>
       <c r="E4" t="n">
         <v>610.08</v>
       </c>
       <c r="F4" t="n">
-        <v>3422</v>
+        <v>1184</v>
       </c>
       <c r="G4" t="n">
-        <v>646</v>
+        <v>876</v>
       </c>
       <c r="H4" t="n">
-        <v>2278</v>
+        <v>3293</v>
       </c>
       <c r="I4" t="n">
-        <v>103</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C5" t="n">
-        <v>2526158329</v>
+        <v>9630806627</v>
       </c>
       <c r="D5" t="n">
-        <v>1277</v>
+        <v>5661</v>
       </c>
       <c r="E5" t="n">
         <v>610.08</v>
       </c>
       <c r="F5" t="n">
-        <v>3422</v>
+        <v>6969</v>
       </c>
       <c r="G5" t="n">
-        <v>646</v>
+        <v>724</v>
       </c>
       <c r="H5" t="n">
-        <v>2278</v>
+        <v>2776</v>
       </c>
       <c r="I5" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -600,38 +600,38 @@
         <v>1841014603</v>
       </c>
       <c r="D6" t="n">
-        <v>2373</v>
+        <v>2789</v>
       </c>
       <c r="E6" t="n">
-        <v>610.08</v>
+        <v>304.94</v>
       </c>
       <c r="F6" t="n">
-        <v>2922</v>
+        <v>1461</v>
       </c>
       <c r="G6" t="n">
-        <v>602</v>
+        <v>301</v>
       </c>
       <c r="H6" t="n">
-        <v>2208</v>
+        <v>1104</v>
       </c>
       <c r="I6" t="n">
-        <v>96</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>525368335</v>
+        <v>495403620</v>
       </c>
       <c r="C7" t="n">
         <v>9628223555</v>
       </c>
       <c r="D7" t="n">
-        <v>3222</v>
+        <v>1676</v>
       </c>
       <c r="E7" t="n">
         <v>610.08</v>
@@ -652,63 +652,63 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C8" t="n">
-        <v>8878077181</v>
+        <v>2526158329</v>
       </c>
       <c r="D8" t="n">
-        <v>1048</v>
+        <v>3286</v>
       </c>
       <c r="E8" t="n">
         <v>610.08</v>
       </c>
       <c r="F8" t="n">
-        <v>1184</v>
+        <v>3422</v>
       </c>
       <c r="G8" t="n">
-        <v>876</v>
+        <v>646</v>
       </c>
       <c r="H8" t="n">
-        <v>3293</v>
+        <v>2278</v>
       </c>
       <c r="I8" t="n">
-        <v>140</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>525368335</v>
+        <v>495403620</v>
       </c>
       <c r="C9" t="n">
-        <v>9811363528</v>
+        <v>8878077181</v>
       </c>
       <c r="D9" t="n">
-        <v>6306</v>
+        <v>1048</v>
       </c>
       <c r="E9" t="n">
         <v>610.08</v>
       </c>
       <c r="F9" t="n">
-        <v>6441</v>
+        <v>1184</v>
       </c>
       <c r="G9" t="n">
-        <v>900</v>
+        <v>876</v>
       </c>
       <c r="H9" t="n">
-        <v>3409</v>
+        <v>3293</v>
       </c>
       <c r="I9" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10">
@@ -724,7 +724,7 @@
         <v>9630806627</v>
       </c>
       <c r="D10" t="n">
-        <v>5679</v>
+        <v>5734</v>
       </c>
       <c r="E10" t="n">
         <v>610.08</v>
@@ -749,34 +749,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>495403620</v>
+        <v>525368335</v>
       </c>
       <c r="C11" t="n">
-        <v>8878077181</v>
+        <v>9811363528</v>
       </c>
       <c r="D11" t="n">
-        <v>1607</v>
+        <v>6473</v>
       </c>
       <c r="E11" t="n">
         <v>610.08</v>
       </c>
       <c r="F11" t="n">
-        <v>1184</v>
+        <v>6441</v>
       </c>
       <c r="G11" t="n">
-        <v>876</v>
+        <v>900</v>
       </c>
       <c r="H11" t="n">
-        <v>3293</v>
+        <v>3409</v>
       </c>
       <c r="I11" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -786,7 +786,7 @@
         <v>9628223555</v>
       </c>
       <c r="D12" t="n">
-        <v>6210</v>
+        <v>546</v>
       </c>
       <c r="E12" t="n">
         <v>610.08</v>
@@ -807,125 +807,125 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C13" t="n">
-        <v>2526158329</v>
+        <v>9811363528</v>
       </c>
       <c r="D13" t="n">
-        <v>5942</v>
+        <v>6222</v>
       </c>
       <c r="E13" t="n">
         <v>610.08</v>
       </c>
       <c r="F13" t="n">
-        <v>3422</v>
+        <v>6441</v>
       </c>
       <c r="G13" t="n">
-        <v>646</v>
+        <v>900</v>
       </c>
       <c r="H13" t="n">
-        <v>2278</v>
+        <v>3409</v>
       </c>
       <c r="I13" t="n">
-        <v>103</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>495817671</v>
+        <v>495403620</v>
       </c>
       <c r="C14" t="n">
-        <v>9630806627</v>
+        <v>9628223555</v>
       </c>
       <c r="D14" t="n">
-        <v>1041</v>
+        <v>1683</v>
       </c>
       <c r="E14" t="n">
         <v>610.08</v>
       </c>
       <c r="F14" t="n">
-        <v>6969</v>
+        <v>6336</v>
       </c>
       <c r="G14" t="n">
-        <v>724</v>
+        <v>745</v>
       </c>
       <c r="H14" t="n">
-        <v>2776</v>
+        <v>2912</v>
       </c>
       <c r="I14" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C15" t="n">
-        <v>1841014603</v>
+        <v>8878077181</v>
       </c>
       <c r="D15" t="n">
-        <v>3169</v>
+        <v>5778</v>
       </c>
       <c r="E15" t="n">
-        <v>304.94</v>
+        <v>610.08</v>
       </c>
       <c r="F15" t="n">
-        <v>1461</v>
+        <v>1184</v>
       </c>
       <c r="G15" t="n">
-        <v>301</v>
+        <v>876</v>
       </c>
       <c r="H15" t="n">
-        <v>1104</v>
+        <v>3293</v>
       </c>
       <c r="I15" t="n">
-        <v>48</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>495817671</v>
       </c>
       <c r="C16" t="n">
-        <v>9628223555</v>
+        <v>9630806627</v>
       </c>
       <c r="D16" t="n">
-        <v>2370</v>
+        <v>2814</v>
       </c>
       <c r="E16" t="n">
         <v>610.08</v>
       </c>
       <c r="F16" t="n">
-        <v>6336</v>
+        <v>6969</v>
       </c>
       <c r="G16" t="n">
-        <v>745</v>
+        <v>724</v>
       </c>
       <c r="H16" t="n">
-        <v>2912</v>
+        <v>2776</v>
       </c>
       <c r="I16" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17">
@@ -941,7 +941,7 @@
         <v>9811363528</v>
       </c>
       <c r="D17" t="n">
-        <v>3431</v>
+        <v>5888</v>
       </c>
       <c r="E17" t="n">
         <v>610.08</v>
@@ -962,203 +962,203 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>495817671</v>
+        <v>525368335</v>
       </c>
       <c r="C18" t="n">
-        <v>9630806627</v>
+        <v>9628223555</v>
       </c>
       <c r="D18" t="n">
-        <v>815</v>
+        <v>2226</v>
       </c>
       <c r="E18" t="n">
         <v>610.08</v>
       </c>
       <c r="F18" t="n">
-        <v>6969</v>
+        <v>6336</v>
       </c>
       <c r="G18" t="n">
-        <v>724</v>
+        <v>745</v>
       </c>
       <c r="H18" t="n">
-        <v>2776</v>
+        <v>2912</v>
       </c>
       <c r="I18" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C19" t="n">
-        <v>8878077181</v>
+        <v>1841014603</v>
       </c>
       <c r="D19" t="n">
-        <v>1607</v>
+        <v>5310</v>
       </c>
       <c r="E19" t="n">
         <v>610.08</v>
       </c>
       <c r="F19" t="n">
-        <v>1184</v>
+        <v>2922</v>
       </c>
       <c r="G19" t="n">
-        <v>876</v>
+        <v>602</v>
       </c>
       <c r="H19" t="n">
-        <v>3293</v>
+        <v>2208</v>
       </c>
       <c r="I19" t="n">
-        <v>140</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>495817671</v>
+        <v>525368335</v>
       </c>
       <c r="C20" t="n">
-        <v>9630806627</v>
+        <v>9811363528</v>
       </c>
       <c r="D20" t="n">
-        <v>1207</v>
+        <v>765</v>
       </c>
       <c r="E20" t="n">
         <v>610.08</v>
       </c>
       <c r="F20" t="n">
-        <v>6969</v>
+        <v>6441</v>
       </c>
       <c r="G20" t="n">
-        <v>724</v>
+        <v>900</v>
       </c>
       <c r="H20" t="n">
-        <v>2776</v>
+        <v>3409</v>
       </c>
       <c r="I20" t="n">
-        <v>116</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>495403620</v>
+        <v>495817671</v>
       </c>
       <c r="C21" t="n">
-        <v>9628223555</v>
+        <v>9630806627</v>
       </c>
       <c r="D21" t="n">
-        <v>5703</v>
+        <v>6578</v>
       </c>
       <c r="E21" t="n">
         <v>610.08</v>
       </c>
       <c r="F21" t="n">
-        <v>6336</v>
+        <v>6969</v>
       </c>
       <c r="G21" t="n">
-        <v>745</v>
+        <v>724</v>
       </c>
       <c r="H21" t="n">
-        <v>2912</v>
+        <v>2776</v>
       </c>
       <c r="I21" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>495403620</v>
+        <v>495817671</v>
       </c>
       <c r="C22" t="n">
-        <v>9628223555</v>
+        <v>9630806627</v>
       </c>
       <c r="D22" t="n">
-        <v>5111</v>
+        <v>3417</v>
       </c>
       <c r="E22" t="n">
         <v>610.08</v>
       </c>
       <c r="F22" t="n">
-        <v>6336</v>
+        <v>6969</v>
       </c>
       <c r="G22" t="n">
-        <v>745</v>
+        <v>724</v>
       </c>
       <c r="H22" t="n">
-        <v>2912</v>
+        <v>2776</v>
       </c>
       <c r="I22" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C23" t="n">
-        <v>9811363528</v>
+        <v>2526158329</v>
       </c>
       <c r="D23" t="n">
-        <v>4202</v>
+        <v>56</v>
       </c>
       <c r="E23" t="n">
         <v>610.08</v>
       </c>
       <c r="F23" t="n">
-        <v>6441</v>
+        <v>3422</v>
       </c>
       <c r="G23" t="n">
-        <v>900</v>
+        <v>646</v>
       </c>
       <c r="H23" t="n">
-        <v>3409</v>
+        <v>2278</v>
       </c>
       <c r="I23" t="n">
-        <v>144</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>495403620</v>
+        <v>525368335</v>
       </c>
       <c r="C24" t="n">
         <v>8878077181</v>
       </c>
       <c r="D24" t="n">
-        <v>1048</v>
+        <v>3989</v>
       </c>
       <c r="E24" t="n">
         <v>610.08</v>
@@ -1179,32 +1179,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C25" t="n">
-        <v>9630806627</v>
+        <v>2526158329</v>
       </c>
       <c r="D25" t="n">
-        <v>4579</v>
+        <v>5942</v>
       </c>
       <c r="E25" t="n">
         <v>610.08</v>
       </c>
       <c r="F25" t="n">
-        <v>6969</v>
+        <v>3422</v>
       </c>
       <c r="G25" t="n">
-        <v>724</v>
+        <v>646</v>
       </c>
       <c r="H25" t="n">
-        <v>2776</v>
+        <v>2278</v>
       </c>
       <c r="I25" t="n">
-        <v>116</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26">
@@ -1214,189 +1214,189 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>525368335</v>
+        <v>495817671</v>
       </c>
       <c r="C26" t="n">
-        <v>8878077181</v>
+        <v>9811363528</v>
       </c>
       <c r="D26" t="n">
-        <v>3989</v>
+        <v>2093</v>
       </c>
       <c r="E26" t="n">
         <v>610.08</v>
       </c>
       <c r="F26" t="n">
-        <v>1184</v>
+        <v>6441</v>
       </c>
       <c r="G26" t="n">
-        <v>876</v>
+        <v>900</v>
       </c>
       <c r="H26" t="n">
-        <v>3293</v>
+        <v>3409</v>
       </c>
       <c r="I26" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>63563817</v>
       </c>
       <c r="C27" t="n">
-        <v>1841014603</v>
+        <v>2526158329</v>
       </c>
       <c r="D27" t="n">
-        <v>2373</v>
+        <v>846</v>
       </c>
       <c r="E27" t="n">
         <v>610.08</v>
       </c>
       <c r="F27" t="n">
-        <v>2922</v>
+        <v>3422</v>
       </c>
       <c r="G27" t="n">
-        <v>602</v>
+        <v>646</v>
       </c>
       <c r="H27" t="n">
-        <v>2208</v>
+        <v>2278</v>
       </c>
       <c r="I27" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>495817671</v>
+        <v>495403620</v>
       </c>
       <c r="C28" t="n">
-        <v>9630806627</v>
+        <v>9628223555</v>
       </c>
       <c r="D28" t="n">
-        <v>3913</v>
+        <v>5467</v>
       </c>
       <c r="E28" t="n">
         <v>610.08</v>
       </c>
       <c r="F28" t="n">
-        <v>6969</v>
+        <v>6336</v>
       </c>
       <c r="G28" t="n">
-        <v>724</v>
+        <v>745</v>
       </c>
       <c r="H28" t="n">
-        <v>2776</v>
+        <v>2912</v>
       </c>
       <c r="I28" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C29" t="n">
-        <v>9811363528</v>
+        <v>1841014603</v>
       </c>
       <c r="D29" t="n">
-        <v>3865</v>
+        <v>2384</v>
       </c>
       <c r="E29" t="n">
         <v>610.08</v>
       </c>
       <c r="F29" t="n">
-        <v>6441</v>
+        <v>2922</v>
       </c>
       <c r="G29" t="n">
-        <v>900</v>
+        <v>602</v>
       </c>
       <c r="H29" t="n">
-        <v>3409</v>
+        <v>2208</v>
       </c>
       <c r="I29" t="n">
-        <v>144</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C30" t="n">
-        <v>2526158329</v>
+        <v>8878077181</v>
       </c>
       <c r="D30" t="n">
-        <v>5700</v>
+        <v>1607</v>
       </c>
       <c r="E30" t="n">
         <v>610.08</v>
       </c>
       <c r="F30" t="n">
-        <v>3422</v>
+        <v>1184</v>
       </c>
       <c r="G30" t="n">
-        <v>646</v>
+        <v>876</v>
       </c>
       <c r="H30" t="n">
-        <v>2278</v>
+        <v>3293</v>
       </c>
       <c r="I30" t="n">
-        <v>103</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>525368335</v>
       </c>
       <c r="C31" t="n">
-        <v>9811363528</v>
+        <v>8878077181</v>
       </c>
       <c r="D31" t="n">
-        <v>4453</v>
+        <v>3989</v>
       </c>
       <c r="E31" t="n">
         <v>610.08</v>
       </c>
       <c r="F31" t="n">
-        <v>6441</v>
+        <v>1184</v>
       </c>
       <c r="G31" t="n">
-        <v>900</v>
+        <v>876</v>
       </c>
       <c r="H31" t="n">
-        <v>3409</v>
+        <v>3293</v>
       </c>
       <c r="I31" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1427,32 +1427,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C33" t="n">
-        <v>8878077181</v>
+        <v>2526158329</v>
       </c>
       <c r="D33" t="n">
-        <v>3989</v>
+        <v>4348</v>
       </c>
       <c r="E33" t="n">
         <v>610.08</v>
       </c>
       <c r="F33" t="n">
-        <v>1184</v>
+        <v>3422</v>
       </c>
       <c r="G33" t="n">
-        <v>876</v>
+        <v>646</v>
       </c>
       <c r="H33" t="n">
-        <v>3293</v>
+        <v>2278</v>
       </c>
       <c r="I33" t="n">
-        <v>140</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34">
@@ -1462,158 +1462,158 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C34" t="n">
-        <v>9811363528</v>
+        <v>2526158329</v>
       </c>
       <c r="D34" t="n">
-        <v>5873</v>
+        <v>770</v>
       </c>
       <c r="E34" t="n">
         <v>610.08</v>
       </c>
       <c r="F34" t="n">
-        <v>6441</v>
+        <v>3422</v>
       </c>
       <c r="G34" t="n">
-        <v>900</v>
+        <v>646</v>
       </c>
       <c r="H34" t="n">
-        <v>3409</v>
+        <v>2278</v>
       </c>
       <c r="I34" t="n">
-        <v>144</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>495817671</v>
+        <v>525368335</v>
       </c>
       <c r="C35" t="n">
-        <v>9630806627</v>
+        <v>9811363528</v>
       </c>
       <c r="D35" t="n">
-        <v>6435</v>
+        <v>5928</v>
       </c>
       <c r="E35" t="n">
         <v>610.08</v>
       </c>
       <c r="F35" t="n">
-        <v>6969</v>
+        <v>6441</v>
       </c>
       <c r="G35" t="n">
-        <v>724</v>
+        <v>900</v>
       </c>
       <c r="H35" t="n">
-        <v>2776</v>
+        <v>3409</v>
       </c>
       <c r="I35" t="n">
-        <v>116</v>
+        <v>144</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C36" t="n">
-        <v>1841014603</v>
+        <v>9811363528</v>
       </c>
       <c r="D36" t="n">
-        <v>5393</v>
+        <v>1958</v>
       </c>
       <c r="E36" t="n">
         <v>610.08</v>
       </c>
       <c r="F36" t="n">
-        <v>2922</v>
+        <v>6441</v>
       </c>
       <c r="G36" t="n">
-        <v>602</v>
+        <v>900</v>
       </c>
       <c r="H36" t="n">
-        <v>2208</v>
+        <v>3409</v>
       </c>
       <c r="I36" t="n">
-        <v>96</v>
+        <v>144</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C37" t="n">
-        <v>2526158329</v>
+        <v>9628223555</v>
       </c>
       <c r="D37" t="n">
-        <v>6014</v>
+        <v>6162</v>
       </c>
       <c r="E37" t="n">
         <v>610.08</v>
       </c>
       <c r="F37" t="n">
-        <v>3422</v>
+        <v>6336</v>
       </c>
       <c r="G37" t="n">
-        <v>646</v>
+        <v>745</v>
       </c>
       <c r="H37" t="n">
-        <v>2278</v>
+        <v>2912</v>
       </c>
       <c r="I37" t="n">
-        <v>103</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>525368335</v>
+        <v>495817671</v>
       </c>
       <c r="C38" t="n">
-        <v>9628223555</v>
+        <v>9630806627</v>
       </c>
       <c r="D38" t="n">
-        <v>3769</v>
+        <v>5431</v>
       </c>
       <c r="E38" t="n">
         <v>610.08</v>
       </c>
       <c r="F38" t="n">
-        <v>6336</v>
+        <v>6969</v>
       </c>
       <c r="G38" t="n">
-        <v>745</v>
+        <v>724</v>
       </c>
       <c r="H38" t="n">
-        <v>2912</v>
+        <v>2776</v>
       </c>
       <c r="I38" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1623,7 +1623,7 @@
         <v>2526158329</v>
       </c>
       <c r="D39" t="n">
-        <v>1262</v>
+        <v>2942</v>
       </c>
       <c r="E39" t="n">
         <v>610.08</v>
@@ -1644,32 +1644,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>495403620</v>
+        <v>495817671</v>
       </c>
       <c r="C40" t="n">
-        <v>9628223555</v>
+        <v>9630806627</v>
       </c>
       <c r="D40" t="n">
-        <v>4046</v>
+        <v>2527</v>
       </c>
       <c r="E40" t="n">
         <v>610.08</v>
       </c>
       <c r="F40" t="n">
-        <v>6336</v>
+        <v>6969</v>
       </c>
       <c r="G40" t="n">
-        <v>745</v>
+        <v>724</v>
       </c>
       <c r="H40" t="n">
-        <v>2912</v>
+        <v>2776</v>
       </c>
       <c r="I40" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
